--- a/artfynd/A 56783-2025 artfynd.xlsx
+++ b/artfynd/A 56783-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>103433572</v>
       </c>
       <c r="B2" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598295.7467452834</v>
+        <v>598296</v>
       </c>
       <c r="R2" t="n">
-        <v>7073055.042694435</v>
+        <v>7073055</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103433588</v>
+        <v>103433593</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598265.4073059537</v>
+        <v>598266</v>
       </c>
       <c r="R3" t="n">
-        <v>7073146.610066957</v>
+        <v>7073147</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,19 +847,9 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103433593</v>
+        <v>103433588</v>
       </c>
       <c r="B4" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598265.4073059537</v>
+        <v>598266</v>
       </c>
       <c r="R4" t="n">
-        <v>7073146.610066957</v>
+        <v>7073147</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,19 +948,9 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 56783-2025 artfynd.xlsx
+++ b/artfynd/A 56783-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103433572</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103433593</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,8 +990,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103433588</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>